--- a/data/BIRO.MI.xlsx
+++ b/data/BIRO.MI.xlsx
@@ -26913,6 +26913,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" s="1" t="n">
+        <v>45940.2916666667</v>
+      </c>
+      <c r="B970" t="n">
+        <v>96400</v>
+      </c>
+      <c r="C970" t="n">
+        <v>0.208000004291534</v>
+      </c>
+      <c r="D970" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="E970" t="n">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="F970" t="n">
+        <v>0.206000000238419</v>
+      </c>
+      <c r="G970" t="s">
+        <v>454</v>
+      </c>
+      <c r="H970" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
